--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.11774742208909</v>
+        <v>6.519133956089477</v>
       </c>
       <c r="D2" t="n">
-        <v>40.92750998711789</v>
+        <v>6.650720372906658</v>
       </c>
       <c r="E2" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F2" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.79159919876178</v>
+        <v>3.54113486979879</v>
       </c>
       <c r="D3" t="n">
-        <v>23.05063548863479</v>
+        <v>3.745728266903154</v>
       </c>
       <c r="E3" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F3" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.12091379397297</v>
+        <v>7.332148491520608</v>
       </c>
       <c r="D4" t="n">
-        <v>46.49016214460201</v>
+        <v>7.554651348497827</v>
       </c>
       <c r="E4" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F4" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.23018717615122</v>
+        <v>6.537405416124574</v>
       </c>
       <c r="D5" t="n">
-        <v>41.69127018489242</v>
+        <v>6.77483140504502</v>
       </c>
       <c r="E5" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F5" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.66273955395356</v>
+        <v>6.445195177517453</v>
       </c>
       <c r="D6" t="n">
-        <v>39.78671137604501</v>
+        <v>6.465340598607313</v>
       </c>
       <c r="E6" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F6" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.4690676345574</v>
+        <v>5.926223490615579</v>
       </c>
       <c r="D7" t="n">
-        <v>36.51776471584517</v>
+        <v>5.93413676632484</v>
       </c>
       <c r="E7" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F7" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.20289595054387</v>
+        <v>6.695470591963379</v>
       </c>
       <c r="D8" t="n">
-        <v>42.41255244039311</v>
+        <v>6.89203977156388</v>
       </c>
       <c r="E8" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F8" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.29183439610399</v>
+        <v>7.847423089366898</v>
       </c>
       <c r="D9" t="n">
-        <v>49.61802451968081</v>
+        <v>8.062928984448131</v>
       </c>
       <c r="E9" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F9" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.06520418645845</v>
+        <v>2.773095680299499</v>
       </c>
       <c r="D10" t="n">
-        <v>17.26626746216959</v>
+        <v>2.805768462602558</v>
       </c>
       <c r="E10" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F10" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.64722516729546</v>
+        <v>5.305174089685512</v>
       </c>
       <c r="D11" t="n">
-        <v>32.89266701320847</v>
+        <v>5.345058389646376</v>
       </c>
       <c r="E11" t="n">
-        <v>9.385131590648728</v>
+        <v>1.525083883480418</v>
       </c>
       <c r="F11" t="n">
-        <v>9.616847433982167</v>
+        <v>1.562737708022102</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
